--- a/2026/Q2/Books information for unlatching upload_ku_2026-02.xlsx
+++ b/2026/Q2/Books information for unlatching upload_ku_2026-02.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="118">
   <si>
     <t xml:space="preserve">Type of Document (Book or Chapter)</t>
   </si>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">African linguistics after COVID</t>
   </si>
   <si>
-    <t xml:space="preserve">Carstens, Vicki &amp; Russell, Katherine R. &amp; Akingbade, Olawale &amp; Morton, Deborah &amp; Diercks, Michael </t>
+    <t xml:space="preserve">Carstens, Vicki; Russell, Katherine R.; Akingbade, Olawale; Morton, Deborah; Diercks, Michael </t>
   </si>
   <si>
     <t xml:space="preserve">LAN009000</t>
@@ -177,9 +177,6 @@
   </si>
   <si>
     <t xml:space="preserve">Mambelli, Gloria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009001</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.19494857</t>
@@ -198,16 +195,10 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/524</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2027</t>
-  </si>
-  <si>
     <t xml:space="preserve">Apprehensional constructions in a cross-linguistic perspective</t>
   </si>
   <si>
-    <t xml:space="preserve">Faller, Martina &amp; Vuillermet, Marine &amp;  Schultze-Berndt, Eva </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009002</t>
+    <t xml:space="preserve">Faller, Martina; Vuillermet, Marine;  Schultze-Berndt, Eva </t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.17977288</t>
@@ -223,9 +214,6 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/530</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2028</t>
-  </si>
-  <si>
     <t xml:space="preserve">Head-Driven Phrase Structure Grammar</t>
   </si>
   <si>
@@ -233,9 +221,6 @@
   </si>
   <si>
     <t xml:space="preserve">Müller, Stefan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009003</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.20538149</t>
@@ -300,19 +285,13 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/535</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2029</t>
-  </si>
-  <si>
     <t xml:space="preserve">Futures of the past</t>
   </si>
   <si>
     <t xml:space="preserve">The diachrony of future constructions across languages</t>
   </si>
   <si>
-    <t xml:space="preserve">Hartmann, Stefan &amp; Schnee, Lena </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009004</t>
+    <t xml:space="preserve">Hartmann, Stefan; Schnee, Lena </t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.19069358</t>
@@ -328,16 +307,10 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/536</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2030</t>
-  </si>
-  <si>
     <t xml:space="preserve">Directional extensions in Chadic languages</t>
   </si>
   <si>
     <t xml:space="preserve">Lovestrand, Joseph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009005</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.19336900</t>
@@ -350,16 +323,10 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/552</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2031</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tracing the history of pronunciation in nineteenth-century English</t>
   </si>
   <si>
     <t xml:space="preserve">Wiemann, Marco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009006</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.20309582</t>
@@ -374,19 +341,13 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/553</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2032</t>
-  </si>
-  <si>
     <t xml:space="preserve">Indigenous languages of the Americas and their structures</t>
   </si>
   <si>
     <t xml:space="preserve">Sounds</t>
   </si>
   <si>
-    <t xml:space="preserve">Saguaro Group, The </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009007</t>
+    <t xml:space="preserve">Saguaro Group, The</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.18384911</t>
@@ -401,16 +362,10 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/563</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2033</t>
-  </si>
-  <si>
     <t xml:space="preserve">Subject focus in French and Spanish</t>
   </si>
   <si>
     <t xml:space="preserve">Cassarà, Alessia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009008</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.19564874</t>
@@ -426,9 +381,6 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/581</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2034</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mood alternations</t>
   </si>
   <si>
@@ -438,9 +390,6 @@
     <t xml:space="preserve">Montero Estebaranz, Raquel</t>
   </si>
   <si>
-    <t xml:space="preserve">LAN009009</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.5281/zenodo.19069652</t>
   </si>
   <si>
@@ -450,9 +399,6 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/582</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2035</t>
-  </si>
-  <si>
     <t xml:space="preserve">Intensitätspartikeln im Deutschen</t>
   </si>
   <si>
@@ -460,9 +406,6 @@
   </si>
   <si>
     <t xml:space="preserve">Schmidt, Jessica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009010</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.18999426</t>
@@ -497,9 +440,6 @@
     <t xml:space="preserve">Weston, Heather</t>
   </si>
   <si>
-    <t xml:space="preserve">LAN009011</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.5281/zenodo.20607629</t>
   </si>
   <si>
@@ -512,9 +452,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://langsci-press.org/catalog/book/590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Language Science Press 2037</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1221,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="12"/>
       <c r="H3" s="9" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>38</v>
@@ -1293,7 +1230,7 @@
         <v>39</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="10" t="n">
@@ -1301,18 +1238,18 @@
       </c>
       <c r="N3" s="13"/>
       <c r="O3" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P3" s="12"/>
       <c r="Q3" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R3" s="14" t="n">
         <v>2</v>
       </c>
       <c r="S3" s="12"/>
       <c r="T3" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U3" s="10" t="s">
         <v>43</v>
@@ -1325,14 +1262,14 @@
       </c>
       <c r="X3" s="16"/>
       <c r="Y3" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AA3" s="16"/>
       <c r="AB3" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1340,17 +1277,17 @@
         <v>33</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="12"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4" s="12"/>
       <c r="H4" s="9" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>38</v>
@@ -1359,7 +1296,7 @@
         <v>39</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="10" t="n">
@@ -1367,18 +1304,18 @@
       </c>
       <c r="N4" s="13"/>
       <c r="O4" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P4" s="12"/>
       <c r="Q4" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R4" s="14" t="n">
         <v>10</v>
       </c>
       <c r="S4" s="12"/>
       <c r="T4" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="U4" s="10" t="s">
         <v>43</v>
@@ -1391,14 +1328,14 @@
       </c>
       <c r="X4" s="16"/>
       <c r="Y4" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AA4" s="16"/>
       <c r="AB4" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1406,19 +1343,19 @@
         <v>33</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="12"/>
       <c r="H5" s="9" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>38</v>
@@ -1427,7 +1364,7 @@
         <v>39</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="10" t="n">
@@ -1435,18 +1372,18 @@
       </c>
       <c r="N5" s="13"/>
       <c r="O5" s="14" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="P5" s="12"/>
       <c r="Q5" s="14" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R5" s="14" t="n">
         <v>17</v>
       </c>
       <c r="S5" s="12"/>
       <c r="T5" s="9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="U5" s="10" t="s">
         <v>43</v>
@@ -1459,14 +1396,14 @@
       </c>
       <c r="X5" s="16"/>
       <c r="Y5" s="10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="AA5" s="16"/>
       <c r="AB5" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1474,19 +1411,19 @@
         <v>33</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="9" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>38</v>
@@ -1495,7 +1432,7 @@
         <v>39</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="10" t="n">
@@ -1503,18 +1440,18 @@
       </c>
       <c r="N6" s="13"/>
       <c r="O6" s="14" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P6" s="12"/>
       <c r="Q6" s="14" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="R6" s="14" t="n">
         <v>3</v>
       </c>
       <c r="S6" s="12"/>
       <c r="T6" s="15" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="U6" s="10" t="s">
         <v>43</v>
@@ -1527,14 +1464,14 @@
       </c>
       <c r="X6" s="16"/>
       <c r="Y6" s="10" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AA6" s="16"/>
       <c r="AB6" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1542,17 +1479,17 @@
         <v>33</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="12"/>
       <c r="E7" s="10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="12"/>
       <c r="H7" s="9" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>38</v>
@@ -1561,7 +1498,7 @@
         <v>39</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="10" t="n">
@@ -1569,7 +1506,7 @@
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="14" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="P7" s="12"/>
       <c r="Q7" s="14" t="s">
@@ -1580,7 +1517,7 @@
       </c>
       <c r="S7" s="12"/>
       <c r="T7" s="15" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="U7" s="10" t="s">
         <v>43</v>
@@ -1593,14 +1530,14 @@
       </c>
       <c r="X7" s="16"/>
       <c r="Y7" s="10" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AA7" s="16"/>
       <c r="AB7" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1608,14 +1545,14 @@
         <v>33</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C8" s="9"/>
       <c r="E8" s="10" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>38</v>
@@ -1632,16 +1569,16 @@
       </c>
       <c r="N8" s="17"/>
       <c r="O8" s="14" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="R8" s="14" t="n">
         <v>4</v>
       </c>
       <c r="T8" s="18" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="U8" s="10" t="s">
         <v>43</v>
@@ -1653,13 +1590,13 @@
         <v>44</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AB8" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1667,17 +1604,17 @@
         <v>33</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>38</v>
@@ -1686,7 +1623,7 @@
         <v>39</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2033</v>
+        <v>2026</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="10" t="n">
@@ -1694,16 +1631,16 @@
       </c>
       <c r="N9" s="17"/>
       <c r="O9" s="14" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R9" s="14" t="n">
         <v>16</v>
       </c>
       <c r="T9" s="18" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="U9" s="10" t="s">
         <v>43</v>
@@ -1715,13 +1652,13 @@
         <v>44</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="AB9" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1729,14 +1666,14 @@
         <v>33</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C10" s="9"/>
       <c r="E10" s="10" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>38</v>
@@ -1745,7 +1682,7 @@
         <v>39</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2034</v>
+        <v>2026</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="10" t="n">
@@ -1753,16 +1690,16 @@
       </c>
       <c r="N10" s="17"/>
       <c r="O10" s="14" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="R10" s="14" t="n">
         <v>9</v>
       </c>
       <c r="T10" s="18" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="U10" s="10" t="s">
         <v>43</v>
@@ -1774,13 +1711,13 @@
         <v>44</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="AB10" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1788,16 +1725,16 @@
         <v>33</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>38</v>
@@ -1806,7 +1743,7 @@
         <v>39</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2035</v>
+        <v>2026</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="10" t="n">
@@ -1814,16 +1751,16 @@
       </c>
       <c r="N11" s="17"/>
       <c r="O11" s="14" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="R11" s="14" t="n">
         <v>8</v>
       </c>
       <c r="T11" s="19" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="U11" s="10" t="s">
         <v>43</v>
@@ -1835,13 +1772,13 @@
         <v>44</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AB11" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1849,16 +1786,16 @@
         <v>33</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>38</v>
@@ -1875,16 +1812,16 @@
       </c>
       <c r="N12" s="17"/>
       <c r="O12" s="14" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="R12" s="14" t="n">
         <v>17</v>
       </c>
       <c r="T12" s="19" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="U12" s="10" t="s">
         <v>43</v>
@@ -1896,13 +1833,13 @@
         <v>44</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="AB12" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1910,16 +1847,16 @@
         <v>33</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>38</v>
@@ -1928,7 +1865,7 @@
         <v>39</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>2037</v>
+        <v>2026</v>
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="10" t="n">
@@ -1936,16 +1873,16 @@
       </c>
       <c r="N13" s="17"/>
       <c r="O13" s="14" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="R13" s="14" t="n">
         <v>17</v>
       </c>
       <c r="T13" s="18" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="U13" s="10" t="s">
         <v>43</v>
@@ -1957,13 +1894,13 @@
         <v>44</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="AB13" s="9" t="s">
         <v>46</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
